--- a/luaran/templates/tables/Table2_Detection_Performance.xlsx
+++ b/luaran/templates/tables/Table2_Detection_Performance.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +27,36 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B9BD5"/>
+        <bgColor rgb="005B9BD5"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +77,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,10 +457,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -436,337 +483,276 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>YOLO Model
-(Medium, 20.1M params)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Best Epoch</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+          <t>YOLOv10
+Medium (20.1M params)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>YOLOv11
+Medium (20.1M params)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>YOLOv12
+Medium (20.1M params)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>mAP@50
 (%)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>mAP@50-95
 (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Precision
 (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Recall
 (%)</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>mAP@50
+(%)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>mAP@50-95
+(%)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Precision
+(%)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Recall
+(%)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>mAP@50
+(%)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>mAP@50-95
+(%)</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Precision
+(%)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Recall
+(%)</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>IML Lifecycle
-(4 stages)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>YOLOv10</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>55</v>
-      </c>
-      <c r="D2" t="n">
-        <v>96.06</v>
-      </c>
-      <c r="E2" t="n">
-        <v>78.43000000000001</v>
-      </c>
-      <c r="F2" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>93.31</v>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>IML Lifecycle (4 stages)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>93.81</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>92.22</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>91.11</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>78.20999999999999</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>86.67</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>YOLOv11</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>84</v>
-      </c>
-      <c r="D3" t="n">
-        <v>96.38</v>
-      </c>
-      <c r="E3" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>91.91</v>
-      </c>
-      <c r="G3" t="n">
-        <v>93.33</v>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MP-IDB Species (4 species)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>90.73</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>62.17</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>91.88</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>89.28</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>YOLOv12</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>43</v>
-      </c>
-      <c r="D4" t="n">
-        <v>96.47</v>
-      </c>
-      <c r="E4" t="n">
-        <v>67.34</v>
-      </c>
-      <c r="F4" t="n">
-        <v>89.02</v>
-      </c>
-      <c r="G4" t="n">
-        <v>88.89</v>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MP-IDB Stages (4 stages)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>94.48</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>96.27</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>92.59</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MP-IDB Species
-(4 species)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>YOLOv10</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>93</v>
-      </c>
-      <c r="D5" t="n">
-        <v>92.77</v>
-      </c>
-      <c r="E5" t="n">
-        <v>59.34</v>
-      </c>
-      <c r="F5" t="n">
-        <v>86.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>89.84999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>YOLOv11</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>84</v>
-      </c>
-      <c r="D6" t="n">
-        <v>93.23999999999999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>61.08</v>
-      </c>
-      <c r="F6" t="n">
-        <v>89.04000000000001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>89.45</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>YOLOv12</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>89</v>
-      </c>
-      <c r="D7" t="n">
-        <v>93.66</v>
-      </c>
-      <c r="E7" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>90.72</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MP-IDB Stages
-(4 stages)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>YOLOv10</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>53</v>
-      </c>
-      <c r="D8" t="n">
-        <v>96</v>
-      </c>
-      <c r="E8" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="F8" t="n">
-        <v>95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>90.48999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>YOLOv11</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" t="n">
-        <v>95.59</v>
-      </c>
-      <c r="E9" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="F9" t="n">
-        <v>93.23999999999999</v>
-      </c>
-      <c r="G9" t="n">
-        <v>88.89</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>YOLOv12</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" t="n">
-        <v>96.28</v>
-      </c>
-      <c r="E10" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="F10" t="n">
-        <v>92.91</v>
-      </c>
-      <c r="G10" t="n">
-        <v>92.59</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MD_2019 Stages
-(3 stages)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>YOLOv10</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>68</v>
-      </c>
-      <c r="D11" t="n">
-        <v>74.69</v>
-      </c>
-      <c r="E11" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="F11" t="n">
-        <v>68.38</v>
-      </c>
-      <c r="G11" t="n">
-        <v>70.39</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>YOLOv11</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>27</v>
-      </c>
-      <c r="D12" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="E12" t="n">
-        <v>54.82</v>
-      </c>
-      <c r="F12" t="n">
-        <v>61</v>
-      </c>
-      <c r="G12" t="n">
-        <v>77.26000000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>YOLOv12</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>35</v>
-      </c>
-      <c r="D13" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="E13" t="n">
-        <v>53.56</v>
-      </c>
-      <c r="F13" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>77.78</v>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MD_2019 Stages (3 stages)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>72.91</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>68.58</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>75.18000000000001</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/luaran/templates/tables/Table2_Detection_Performance.xlsx
+++ b/luaran/templates/tables/Table2_Detection_Performance.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -473,6 +473,9 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -483,20 +486,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>YOLOv10
-Medium (20.1M params)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>YOLOv11
-Medium (20.1M params)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>YOLOv12
-Medium (20.1M params)</t>
+          <t>YOLOv10</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>YOLOv11</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>YOLOv12</t>
         </is>
       </c>
     </row>
@@ -528,50 +528,68 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>Time
+(min)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>mAP@50
 (%)</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>mAP@50-95
 (%)</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Precision
 (%)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Recall
 (%)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Time
+(min)</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>mAP@50
 (%)</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>mAP@50-95
 (%)</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Precision
 (%)</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Recall
 (%)</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Time
+(min)</t>
         </is>
       </c>
     </row>
@@ -594,28 +612,37 @@
         <v>92.22</v>
       </c>
       <c r="F3" s="5" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G3" s="5" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="H3" s="5" t="n">
         <v>77.76000000000001</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="I3" s="5" t="n">
         <v>91.91</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="J3" s="5" t="n">
         <v>91.11</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="K3" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L3" s="5" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="M3" s="5" t="n">
         <v>78.20999999999999</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>92.2</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="O3" s="5" t="n">
         <v>86.67</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>7.55</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
@@ -637,28 +664,37 @@
         <v>90.73</v>
       </c>
       <c r="F4" s="5" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="H4" s="5" t="n">
         <v>62.17</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>86.52</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="J4" s="5" t="n">
         <v>91.88</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="K4" s="5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="L4" s="5" t="n">
         <v>92.72</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>62.25</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="O4" s="5" t="n">
         <v>89.28</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>4.71</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
@@ -680,28 +716,37 @@
         <v>93.12</v>
       </c>
       <c r="F5" s="5" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>94.48</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <v>60.34</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>93.15000000000001</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>88.36</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5" s="5" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>96.27</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>61.53</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>92.91</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="O5" s="5" t="n">
         <v>92.59</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>5.79</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -723,35 +768,44 @@
         <v>71.05</v>
       </c>
       <c r="F6" s="5" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>72.91</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <v>57.71</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>68.58</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>75.7</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="L6" s="5" t="n">
         <v>71.12</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>56.93</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>65.92</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="O6" s="5" t="n">
         <v>75.18000000000001</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>13.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
